--- a/Results/df_mnd_miro_pla_sequential_trial_gap_weighted.xlsx
+++ b/Results/df_mnd_miro_pla_sequential_trial_gap_weighted.xlsx
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="F2" t="n">
-        <v>0.97</v>
+        <v>0.38</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03328558877587979</v>
+        <v>1.085249951097651e-09</v>
       </c>
     </row>
     <row r="3">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.67</v>
+        <v>0.24</v>
       </c>
       <c r="E3" t="n">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.97</v>
+        <v>0.39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03400995985023331</v>
+        <v>3.030479801343168e-09</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.68</v>
+        <v>0.24</v>
       </c>
       <c r="E4" t="n">
-        <v>0.48</v>
+        <v>0.15</v>
       </c>
       <c r="F4" t="n">
-        <v>0.98</v>
+        <v>0.39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03875872787435428</v>
+        <v>1.935494603183413e-09</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3.52</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2313382528092207</v>
+        <v>0.08001015728445678</v>
       </c>
     </row>
   </sheetData>
